--- a/Member.xlsx
+++ b/Member.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a225a4cd7e80232/Wasawat/Etheria/gvgplaner/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="70" documentId="11_8947612F1371E0CEEB3B98154B88467870408069" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F8E1E26-7C93-4B4F-8AE3-8539D039EC26}"/>
+  <xr:revisionPtr revIDLastSave="72" documentId="11_8947612F1371E0CEEB3B98154B88467870408069" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5054D904-D675-470D-A036-427714FEE85E}"/>
   <bookViews>
-    <workbookView xWindow="12552" yWindow="168" windowWidth="10488" windowHeight="12072" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Members" sheetId="1" r:id="rId1"/>
@@ -128,10 +128,10 @@
     <t>CloverZ</t>
   </si>
   <si>
-    <t>GMMFAFA</t>
-  </si>
-  <si>
     <t>หอมหอย</t>
+  </si>
+  <si>
+    <t>DUCKs</t>
   </si>
 </sst>
 </file>
@@ -479,7 +479,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -514,7 +514,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -618,7 +618,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">

--- a/Member.xlsx
+++ b/Member.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a225a4cd7e80232/Wasawat/Etheria/gvgplaner/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="72" documentId="11_8947612F1371E0CEEB3B98154B88467870408069" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5054D904-D675-470D-A036-427714FEE85E}"/>
+  <xr:revisionPtr revIDLastSave="83" documentId="11_8947612F1371E0CEEB3B98154B88467870408069" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F4A6DA8-73A5-4F8F-837C-09DB2EC092E6}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -74,12 +74,6 @@
     <t>SekiSaySo</t>
   </si>
   <si>
-    <t>soutax</t>
-  </si>
-  <si>
-    <t>Catzilla</t>
-  </si>
-  <si>
     <t>Mkay</t>
   </si>
   <si>
@@ -89,9 +83,6 @@
     <t>akirA</t>
   </si>
   <si>
-    <t>ActiasLuna</t>
-  </si>
-  <si>
     <t>PaTTz</t>
   </si>
   <si>
@@ -101,9 +92,6 @@
     <t>WCRz</t>
   </si>
   <si>
-    <t>NeerZX</t>
-  </si>
-  <si>
     <t>RRXIITH</t>
   </si>
   <si>
@@ -132,6 +120,18 @@
   </si>
   <si>
     <t>DUCKs</t>
+  </si>
+  <si>
+    <t>N•Force1</t>
+  </si>
+  <si>
+    <t>SwallowTaiL</t>
+  </si>
+  <si>
+    <t>Souta メ</t>
+  </si>
+  <si>
+    <t>iCatzilla</t>
   </si>
 </sst>
 </file>
@@ -484,13 +484,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
@@ -498,7 +498,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -514,7 +514,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -530,7 +530,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -538,7 +538,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -546,7 +546,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -554,7 +554,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -562,7 +562,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
@@ -570,7 +570,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -578,7 +578,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
@@ -586,7 +586,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
@@ -594,7 +594,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
@@ -602,7 +602,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
@@ -610,7 +610,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
@@ -618,7 +618,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
@@ -626,7 +626,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
@@ -634,7 +634,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
@@ -642,7 +642,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
@@ -650,7 +650,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
@@ -674,7 +674,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
@@ -682,7 +682,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
@@ -690,7 +690,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
@@ -698,7 +698,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
@@ -706,7 +706,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
@@ -714,7 +714,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
@@ -722,7 +722,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
@@ -734,8 +734,8 @@
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B10:B31">
-    <sortCondition ref="B31"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B6:B31">
+    <sortCondition ref="B6:B31"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Member.xlsx
+++ b/Member.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a225a4cd7e80232/Wasawat/Etheria/gvgplaner/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="83" documentId="11_8947612F1371E0CEEB3B98154B88467870408069" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F4A6DA8-73A5-4F8F-837C-09DB2EC092E6}"/>
+  <xr:revisionPtr revIDLastSave="84" documentId="11_8947612F1371E0CEEB3B98154B88467870408069" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D4553A0-4D56-45B5-9DA5-A355D9EBE357}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2652" yWindow="840" windowWidth="20388" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Members" sheetId="1" r:id="rId1"/>
@@ -86,9 +86,6 @@
     <t>PaTTz</t>
   </si>
   <si>
-    <t>Axion</t>
-  </si>
-  <si>
     <t>WCRz</t>
   </si>
   <si>
@@ -132,6 +129,9 @@
   </si>
   <si>
     <t>iCatzilla</t>
+  </si>
+  <si>
+    <t>Ducks</t>
   </si>
 </sst>
 </file>
@@ -484,13 +484,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
@@ -498,7 +498,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -514,7 +514,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -538,7 +538,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -546,7 +546,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -586,7 +586,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
@@ -602,7 +602,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
@@ -610,7 +610,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
@@ -618,7 +618,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
@@ -626,7 +626,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
@@ -650,7 +650,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
@@ -690,7 +690,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
@@ -706,7 +706,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
@@ -714,7 +714,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
@@ -722,7 +722,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">

--- a/Member.xlsx
+++ b/Member.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a225a4cd7e80232/Wasawat/Etheria/gvgplaner/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="84" documentId="11_8947612F1371E0CEEB3B98154B88467870408069" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D4553A0-4D56-45B5-9DA5-A355D9EBE357}"/>
+  <xr:revisionPtr revIDLastSave="85" documentId="11_8947612F1371E0CEEB3B98154B88467870408069" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22CCE8F6-7A80-42C7-9862-CE8FA77B6E3F}"/>
   <bookViews>
     <workbookView xWindow="2652" yWindow="840" windowWidth="20388" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -546,7 +546,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>32</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -554,7 +554,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -562,7 +562,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
@@ -570,7 +570,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -578,7 +578,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
@@ -586,7 +586,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
@@ -594,7 +594,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">

--- a/Member.xlsx
+++ b/Member.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a225a4cd7e80232/Wasawat/Etheria/gvgplaner/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="85" documentId="11_8947612F1371E0CEEB3B98154B88467870408069" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22CCE8F6-7A80-42C7-9862-CE8FA77B6E3F}"/>
+  <xr:revisionPtr revIDLastSave="95" documentId="11_8947612F1371E0CEEB3B98154B88467870408069" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C94F091F-2D1E-4B29-9AB2-10DDBEEE0F63}"/>
   <bookViews>
-    <workbookView xWindow="2652" yWindow="840" windowWidth="20388" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Members" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>ID</t>
   </si>
@@ -105,12 +105,6 @@
   </si>
   <si>
     <t>No</t>
-  </si>
-  <si>
-    <t>Luminus</t>
-  </si>
-  <si>
-    <t>CloverZ</t>
   </si>
   <si>
     <t>หอมหอย</t>
@@ -475,7 +469,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.44140625" bestFit="1" customWidth="1"/>
@@ -514,7 +508,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -578,7 +572,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
@@ -586,7 +580,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
@@ -594,7 +588,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
@@ -602,7 +596,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
@@ -610,7 +604,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
@@ -618,7 +612,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
@@ -626,7 +620,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
@@ -634,7 +628,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
@@ -642,7 +636,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
@@ -650,7 +644,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
@@ -658,7 +652,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
@@ -666,7 +660,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
@@ -674,7 +668,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
@@ -682,7 +676,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
@@ -690,7 +684,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
@@ -698,7 +692,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
@@ -706,7 +700,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
@@ -714,28 +708,12 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A30">
-        <v>29</v>
-      </c>
-      <c r="B30" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A31">
-        <v>30</v>
-      </c>
-      <c r="B31" t="s">
         <v>9</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B6:B31">
-    <sortCondition ref="B6:B31"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B6:B29">
+    <sortCondition ref="B6:B29"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Member.xlsx
+++ b/Member.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a225a4cd7e80232/Wasawat/Etheria/gvgplaner/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="95" documentId="11_8947612F1371E0CEEB3B98154B88467870408069" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C94F091F-2D1E-4B29-9AB2-10DDBEEE0F63}"/>
+  <xr:revisionPtr revIDLastSave="125" documentId="11_8947612F1371E0CEEB3B98154B88467870408069" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BCA249F6-36E9-44E2-ADD9-A29A4FC5DF24}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="54">
   <si>
     <t>ID</t>
   </si>
@@ -126,6 +126,75 @@
   </si>
   <si>
     <t>Ducks</t>
+  </si>
+  <si>
+    <t>ActiasLuna</t>
+  </si>
+  <si>
+    <t>ALOHa</t>
+  </si>
+  <si>
+    <t>ซี</t>
+  </si>
+  <si>
+    <t>เหมา</t>
+  </si>
+  <si>
+    <t>สา</t>
+  </si>
+  <si>
+    <t>นิค</t>
+  </si>
+  <si>
+    <t>แพร</t>
+  </si>
+  <si>
+    <t>หนึ่ง</t>
+  </si>
+  <si>
+    <t>เจม</t>
+  </si>
+  <si>
+    <t>มอส</t>
+  </si>
+  <si>
+    <t>บลู</t>
+  </si>
+  <si>
+    <t>ชัย</t>
+  </si>
+  <si>
+    <t>เป็ด</t>
+  </si>
+  <si>
+    <t>ต้น</t>
+  </si>
+  <si>
+    <t>Liam</t>
+  </si>
+  <si>
+    <t>เกม</t>
+  </si>
+  <si>
+    <t>แน็ค</t>
+  </si>
+  <si>
+    <t>แบล็ค</t>
+  </si>
+  <si>
+    <t>พัท</t>
+  </si>
+  <si>
+    <t>โอ๊ต</t>
+  </si>
+  <si>
+    <t>เซกิ</t>
+  </si>
+  <si>
+    <t>ลีโอ</t>
+  </si>
+  <si>
+    <t>แจ็ค</t>
   </si>
 </sst>
 </file>
@@ -469,7 +538,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.44140625" bestFit="1" customWidth="1"/>
@@ -494,6 +563,9 @@
       <c r="B2" t="s">
         <v>20</v>
       </c>
+      <c r="C2" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3">
@@ -502,6 +574,9 @@
       <c r="B3" t="s">
         <v>5</v>
       </c>
+      <c r="C3" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4">
@@ -510,6 +585,9 @@
       <c r="B4" t="s">
         <v>24</v>
       </c>
+      <c r="C4" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5">
@@ -518,13 +596,19 @@
       <c r="B5" t="s">
         <v>10</v>
       </c>
+      <c r="C5" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>31</v>
+      </c>
+      <c r="C6" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -532,7 +616,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>32</v>
+      </c>
+      <c r="C7" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -540,7 +627,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>1</v>
+        <v>15</v>
+      </c>
+      <c r="C8" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -548,7 +638,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>3</v>
+        <v>19</v>
+      </c>
+      <c r="C9" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -556,7 +649,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
@@ -564,7 +657,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>3</v>
+      </c>
+      <c r="C11" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -572,7 +668,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>7</v>
+        <v>2</v>
+      </c>
+      <c r="C12" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
@@ -580,7 +679,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>30</v>
+        <v>14</v>
+      </c>
+      <c r="C13" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
@@ -588,7 +690,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
@@ -596,7 +698,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="C15" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
@@ -604,116 +709,171 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+      <c r="C16" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="C17" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="C18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="C19" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+      <c r="C21" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+      <c r="C22" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+      <c r="C23" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+      <c r="C24" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+      <c r="C26" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+      <c r="C27" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" t="s">
+        <v>27</v>
+      </c>
+      <c r="C29" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>17</v>
+      </c>
+      <c r="C30" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
         <v>9</v>
       </c>
+      <c r="C31" t="s">
+        <v>53</v>
+      </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B6:B29">
-    <sortCondition ref="B6:B29"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B8:B31">
+    <sortCondition ref="B8:B31"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Member.xlsx
+++ b/Member.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a225a4cd7e80232/Wasawat/Etheria/gvgplaner/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="125" documentId="11_8947612F1371E0CEEB3B98154B88467870408069" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BCA249F6-36E9-44E2-ADD9-A29A4FC5DF24}"/>
+  <xr:revisionPtr revIDLastSave="155" documentId="11_8947612F1371E0CEEB3B98154B88467870408069" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D342D516-41E5-4981-9EF9-52E20300EA6F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="55">
   <si>
     <t>ID</t>
   </si>
@@ -122,9 +122,6 @@
     <t>Souta メ</t>
   </si>
   <si>
-    <t>iCatzilla</t>
-  </si>
-  <si>
     <t>Ducks</t>
   </si>
   <si>
@@ -134,67 +131,73 @@
     <t>ALOHa</t>
   </si>
   <si>
-    <t>ซี</t>
-  </si>
-  <si>
-    <t>เหมา</t>
-  </si>
-  <si>
-    <t>สา</t>
-  </si>
-  <si>
-    <t>นิค</t>
-  </si>
-  <si>
-    <t>แพร</t>
-  </si>
-  <si>
-    <t>หนึ่ง</t>
-  </si>
-  <si>
-    <t>เจม</t>
-  </si>
-  <si>
-    <t>มอส</t>
-  </si>
-  <si>
-    <t>บลู</t>
-  </si>
-  <si>
-    <t>ชัย</t>
-  </si>
-  <si>
-    <t>เป็ด</t>
-  </si>
-  <si>
-    <t>ต้น</t>
-  </si>
-  <si>
-    <t>Liam</t>
-  </si>
-  <si>
-    <t>เกม</t>
-  </si>
-  <si>
-    <t>แน็ค</t>
-  </si>
-  <si>
-    <t>แบล็ค</t>
-  </si>
-  <si>
-    <t>พัท</t>
-  </si>
-  <si>
-    <t>โอ๊ต</t>
-  </si>
-  <si>
-    <t>เซกิ</t>
-  </si>
-  <si>
-    <t>ลีโอ</t>
-  </si>
-  <si>
-    <t>แจ็ค</t>
+    <t>K.ซี</t>
+  </si>
+  <si>
+    <t>K.เกา</t>
+  </si>
+  <si>
+    <t>K.เหมา</t>
+  </si>
+  <si>
+    <t>K.สา</t>
+  </si>
+  <si>
+    <t>K.นิค</t>
+  </si>
+  <si>
+    <t>K.แพร</t>
+  </si>
+  <si>
+    <t>K.หนึ่ง</t>
+  </si>
+  <si>
+    <t>K.เจม</t>
+  </si>
+  <si>
+    <t>K.มอส</t>
+  </si>
+  <si>
+    <t>K.บลู</t>
+  </si>
+  <si>
+    <t>K.ชัย</t>
+  </si>
+  <si>
+    <t>K.เป็ด</t>
+  </si>
+  <si>
+    <t>K.ต้น</t>
+  </si>
+  <si>
+    <t>K.Liam</t>
+  </si>
+  <si>
+    <t>K.เกม</t>
+  </si>
+  <si>
+    <t>K.แน็ค</t>
+  </si>
+  <si>
+    <t>K.แบล็ค</t>
+  </si>
+  <si>
+    <t>K.พัท</t>
+  </si>
+  <si>
+    <t>K.โอ๊ต</t>
+  </si>
+  <si>
+    <t>K.เซกิ</t>
+  </si>
+  <si>
+    <t>K.ลีโอ</t>
+  </si>
+  <si>
+    <t>K.แจ็ค</t>
+  </si>
+  <si>
+    <t>Catzilla</t>
   </si>
 </sst>
 </file>
@@ -564,7 +567,7 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -575,7 +578,7 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -605,7 +608,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C6" t="s">
         <v>36</v>
@@ -616,7 +619,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C7" t="s">
         <v>37</v>
@@ -679,10 +682,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="C13" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
@@ -690,7 +693,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>7</v>
+        <v>14</v>
+      </c>
+      <c r="C14" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
@@ -698,10 +704,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>30</v>
-      </c>
-      <c r="C15" t="s">
-        <v>43</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
@@ -709,7 +712,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C16" t="s">
         <v>43</v>
@@ -720,10 +723,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">

--- a/Member.xlsx
+++ b/Member.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a225a4cd7e80232/Wasawat/Etheria/gvgplaner/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="155" documentId="11_8947612F1371E0CEEB3B98154B88467870408069" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D342D516-41E5-4981-9EF9-52E20300EA6F}"/>
+  <xr:revisionPtr revIDLastSave="159" documentId="11_8947612F1371E0CEEB3B98154B88467870408069" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{663A376D-B806-41CD-9C33-E7A1C9AACFE3}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="56">
   <si>
     <t>ID</t>
   </si>
@@ -74,9 +74,6 @@
     <t>SekiSaySo</t>
   </si>
   <si>
-    <t>Mkay</t>
-  </si>
-  <si>
     <t>Chai</t>
   </si>
   <si>
@@ -198,6 +195,12 @@
   </si>
   <si>
     <t>Catzilla</t>
+  </si>
+  <si>
+    <t>GGood</t>
+  </si>
+  <si>
+    <t>K.กาย</t>
   </si>
 </sst>
 </file>
@@ -550,13 +553,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
@@ -564,10 +567,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -578,7 +581,7 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -586,10 +589,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -600,7 +603,7 @@
         <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -608,10 +611,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -619,7 +622,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
         <v>37</v>
@@ -630,10 +633,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -641,10 +644,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -663,7 +666,7 @@
         <v>3</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -674,7 +677,7 @@
         <v>2</v>
       </c>
       <c r="C12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
@@ -682,10 +685,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C13" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
@@ -693,10 +696,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
@@ -712,10 +715,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -723,10 +726,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
@@ -734,10 +737,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="C18" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
@@ -745,10 +748,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="C19" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
@@ -756,7 +759,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>13</v>
+        <v>6</v>
+      </c>
+      <c r="C20" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
@@ -764,10 +770,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C21" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
@@ -778,7 +784,7 @@
         <v>11</v>
       </c>
       <c r="C22" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
@@ -789,7 +795,7 @@
         <v>8</v>
       </c>
       <c r="C23" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
@@ -797,10 +803,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C24" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
@@ -816,10 +822,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C26" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
@@ -830,7 +836,7 @@
         <v>12</v>
       </c>
       <c r="C27" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
@@ -838,7 +844,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
@@ -846,10 +852,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C29" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
@@ -857,10 +863,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C30" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
@@ -871,12 +877,12 @@
         <v>9</v>
       </c>
       <c r="C31" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B8:B31">
-    <sortCondition ref="B8:B31"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B6:C31">
+    <sortCondition ref="B6:B31"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Member.xlsx
+++ b/Member.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a225a4cd7e80232/Wasawat/Etheria/gvgplaner/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="159" documentId="11_8947612F1371E0CEEB3B98154B88467870408069" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{663A376D-B806-41CD-9C33-E7A1C9AACFE3}"/>
+  <xr:revisionPtr revIDLastSave="162" documentId="11_8947612F1371E0CEEB3B98154B88467870408069" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0A983FE0-55AF-44EF-B319-BCF8EC95C822}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="57">
   <si>
     <t>ID</t>
   </si>
@@ -201,6 +201,9 @@
   </si>
   <si>
     <t>K.กาย</t>
+  </si>
+  <si>
+    <t>K.แซน</t>
   </si>
 </sst>
 </file>
@@ -657,6 +660,9 @@
       <c r="B10" t="s">
         <v>1</v>
       </c>
+      <c r="C10" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11">
